--- a/resultados/relatorio_final.xlsx
+++ b/resultados/relatorio_final.xlsx
@@ -179,8 +179,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Legenda_Fase_6" displayName="Legenda_Fase_6" ref="A19:D26" headerRowCount="1">
-  <autoFilter ref="A19:D26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Legenda_Fase_6" displayName="Legenda_Fase_6" ref="A19:D25" headerRowCount="1">
+  <autoFilter ref="A19:D25"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Legenda_Fase_1" displayName="Legenda_Fase_1" ref="A19:D30" headerRowCount="1">
-  <autoFilter ref="A19:D30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Legenda_Fase_1" displayName="Legenda_Fase_1" ref="A19:D28" headerRowCount="1">
+  <autoFilter ref="A19:D28"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
@@ -220,8 +220,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Legenda_Fase_2" displayName="Legenda_Fase_2" ref="A19:D26" headerRowCount="1">
-  <autoFilter ref="A19:D26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Legenda_Fase_2" displayName="Legenda_Fase_2" ref="A19:D34" headerRowCount="1">
+  <autoFilter ref="A19:D34"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -660,12 +660,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CAD5103</t>
+          <t>CIN7141</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Administração I</t>
+          <t>Lógica Instrumental I</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -695,49 +695,49 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.1830-4</t>
+          <t>5.2020-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE129</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Monica Scoz Mendes</t>
+          <t>Ilson Wilmar Rodrigues Filho</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CAD5103</t>
+          <t>CIN7143</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>01342D</t>
+          <t>01342C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Administração I</t>
+          <t>Empreendedorismo I</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,49 +757,49 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.1830-4</t>
+          <t>3.2020-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>EF1-EFI402</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>A contratar</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CIN7141</t>
+          <t>CIN7144</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>01342C</t>
+          <t>01342</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lógica Instrumental I</t>
+          <t>Tutoria Acadêmica I</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -819,49 +819,49 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.1830-2</t>
+          <t>2.1510-1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Ilson Wilmar Rodrigues Filho</t>
+          <t>Ricardo Alexandre Reinaldo de Moraes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CIN7143</t>
+          <t>CIN7145</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>01342C</t>
+          <t>01342</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Empreendedorismo I</t>
+          <t>Gestão da Informação</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -886,49 +886,49 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.2020-2</t>
+          <t>2.1620-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-103 C</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>Nathalia Berger Werlang</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CIN7144</t>
+          <t>CIN7201</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>01342</t>
+          <t>02342A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tutoria Acadêmica I</t>
+          <t>Sistemas de Organização do Conhecimento</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1ª Fase</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -943,54 +943,54 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.1510-1</t>
+          <t>6.0820-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-004 D</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ricardo Alexandre Reinaldo de Moraes</t>
+          <t>Mariana Xavier de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CIN7145</t>
+          <t>CIN7201</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>01342</t>
+          <t>02342C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Gestão da Informação</t>
+          <t>Sistemas de Organização do Conhecimento</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1ª Fase</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1000,54 +1000,54 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.1620-2</t>
+          <t>6.1830-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>EF1-EFI405</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Nathalia Berger Werlang</t>
+          <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CIN7201</t>
+          <t>CIN7202</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>02342C</t>
+          <t>02342A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sistemas de Organização do Conhecimento</t>
+          <t>Sociedade da Informação</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1067,39 +1067,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.1830-4</t>
+          <t>3.0820-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Mariana Xavier de Oliveira</t>
+          <t>Enrique Muriel Torrado</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CIN7204</t>
+          <t>CIN7202</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tutoria Acadêmica II</t>
+          <t>Sociedade da Informação</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1129,54 +1129,54 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.1710-1</t>
+          <t>4.2020-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>CED-D109</t>
+          <t>EF1-EFI305</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ricardo Alexandre Reinaldo de Moraes</t>
+          <t>Enrique Muriel Torrado</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CIN7301</t>
+          <t>CIN7203</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>03342A</t>
+          <t>02342A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Introdução à Representação Temática</t>
+          <t>Ética Profissional</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3ª Fase</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1201,44 +1201,44 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.1010-2</t>
+          <t>5.0730-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-004 D</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Mariana Xavier de Oliveira</t>
+          <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CIN7301</t>
+          <t>CIN7203</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>03342C</t>
+          <t>02342C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Introdução à Representação Temática</t>
+          <t>Ética Profissional</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3ª Fase</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1263,44 +1263,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.2020-2</t>
+          <t>4.1830-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>EF1-EFI304</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>A contratar</t>
+          <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CIN7302</t>
+          <t>CIN7204</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>03342A</t>
+          <t>02342C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Introdução à Representação Descritiva</t>
+          <t>Tutoria Acadêmica II</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3ª Fase</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1315,54 +1315,54 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6.1010-2</t>
+          <t>4.1710-1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>CED-105 B</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Maria Zanela</t>
+          <t>Ricardo Alexandre Reinaldo de Moraes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CIN7302</t>
+          <t>CIN7205</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>03342C</t>
+          <t>02342B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Introdução à Representação Descritiva</t>
+          <t>Recuperação da Informação</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3ª Fase</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1377,54 +1377,54 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5.1830-2</t>
+          <t>2.1420-4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-516B</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Edgar Bisset Alvarez</t>
+          <t>A contratar</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CIN7303</t>
+          <t>CIN7206</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>03342A</t>
+          <t>02342A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Metodologia da Pesquisa</t>
+          <t>Fontes Gerais de Informação</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3ª Fase</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1449,44 +1449,44 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.1010-2</t>
+          <t>2.0820-2 | 3.1010-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>CED-102 C | CED-102 C</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Luis Roberto Sousa Mendes</t>
+          <t>Aline Carmes Krüger</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CIN7303</t>
+          <t>CIN7206</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>03342C</t>
+          <t>02342C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Metodologia da Pesquisa</t>
+          <t>Fontes Gerais de Informação</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3ª Fase</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1511,29 +1511,29 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.2020-2</t>
+          <t>3.1830-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>CED-103 C</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Maria Zanela</t>
+          <t>Patricia da Silva Neubert</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CIN7304</t>
+          <t>CIN7301</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Introdução à Bancos de Dados</t>
+          <t>Introdução à Representação Temática</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1578,24 +1578,24 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>CFH-1FH330</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Gustavo Medeiros de Araújo</t>
+          <t>Mariana Xavier de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CIN7304</t>
+          <t>CIN7301</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Introdução à Bancos de Dados</t>
+          <t>Introdução à Representação Temática</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1635,29 +1635,29 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5.2020-2</t>
+          <t>5.1830-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>CED-102 C</t>
+          <t>EF1-EFI304</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Gustavo Medeiros de Araújo</t>
+          <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CIN7306</t>
+          <t>CIN7302</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Competência Informacional</t>
+          <t>Introdução à Representação Descritiva</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>6.0820-2</t>
+          <t>6.1010-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1707,19 +1707,19 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Maria Zanela</t>
+          <t>Elizete Vieira Vitorino e Maria Zanela</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CIN7306</t>
+          <t>CIN7302</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Competência Informacional</t>
+          <t>Introdução à Representação Descritiva</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1754,44 +1754,44 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.1830-2</t>
+          <t>3.2020-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>CED-103 C</t>
+          <t>EF1-EFI401</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Maria Zanela</t>
+          <t>Mariana Xavier de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CIN7309</t>
+          <t>CIN7303</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>02342C</t>
+          <t>03342A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Gestão de Processos Organizacionais</t>
+          <t>Metodologia da Pesquisa</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1811,49 +1811,49 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4.1830-4</t>
+          <t>2.1010-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>A contratar</t>
+          <t>Luis Roberto Sousa Mendes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CIN7309</t>
+          <t>CIN7303</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>03342A</t>
+          <t>03342C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Gestão de Processos Organizacionais</t>
+          <t>Metodologia da Pesquisa</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1873,54 +1873,54 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4.0820-4</t>
+          <t>2.2020-2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>CED-103 C</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>A contratar</t>
+          <t>Maria Zanela e Elizete Vieira Vitorino</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CIN7401</t>
+          <t>CIN7304</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>04342A</t>
+          <t>03342A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Estudos Métricos da Informação</t>
+          <t>Introdução à Bancos de Dados</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4ª Fase</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1945,44 +1945,44 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.0820-4</t>
+          <t>4.0820-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>CED-103 C</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Adilson Luiz Pinto</t>
+          <t>Gustavo Medeiros de Araújo</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CIN7401</t>
+          <t>CIN7304</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>04342C</t>
+          <t>03342C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Estudos Métricos da Informação</t>
+          <t>Introdução à Bancos de Dados</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4ª Fase</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2007,44 +2007,44 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.1830-4</t>
+          <t>5.2020-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>CED-103 C</t>
+          <t>CED-102 C</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Adilson Luiz Pinto</t>
+          <t>Gustavo Medeiros de Araújo</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CIN7402</t>
+          <t>CIN7306</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>04342A</t>
+          <t>03342A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Editoração Científica</t>
+          <t>Competência Informacional</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4ª Fase</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2069,44 +2069,44 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>6.1010-2</t>
+          <t>6.0820-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Enrique Muriel Torrado</t>
+          <t>Maria Zanela e Elizete Vieira Vitorino</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CIN7402</t>
+          <t>CIN7306</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>04342C</t>
+          <t>03342C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Editoração Científica</t>
+          <t>Competência Informacional</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4ª Fase</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>6.1830-2</t>
+          <t>2.1830-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2141,34 +2141,34 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Enrique Muriel Torrado</t>
+          <t>Maria Zanela e Elizete Vieira Vitorino</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CIN7403</t>
+          <t>CIN7309</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>04342C</t>
+          <t>03342A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Acessibilidade e Inclusão Digital</t>
+          <t>Gestão de Processos Organizacionais</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4ª Fase</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2183,54 +2183,54 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2.1710-1 | 4.1710-1</t>
+          <t>3.1010-2 | 4.1010-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>CED-LBPREV | CED-LBPREV</t>
+          <t>CED-LBTEC | CED-LBTEC</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Ilson Wilmar Rodrigues Filho</t>
+          <t>Rogerio da Silva Nunes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CIN7404</t>
+          <t>CIN7309</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>04342A</t>
+          <t>03342C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Planejamento Estratégico</t>
+          <t>Gestão de Processos Organizacionais</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>4ª Fase</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2255,39 +2255,39 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4.0730-1 | 6.0730-1</t>
+          <t>3.1830-2 | 4.1830-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>CED-103 C | CED-103 C</t>
+          <t>CED-LBTEC | CED-LBTEC</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Maria Zanela</t>
+          <t>Rogerio da Silva Nunes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CIN7404</t>
+          <t>CIN7401</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>04342C</t>
+          <t>04342A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Planejamento Estratégico</t>
+          <t>Estudos Métricos da Informação</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2317,39 +2317,39 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>6.2020-2</t>
+          <t>2.0820-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>CED-103 C</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>Adilson Luiz Pinto</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CIN7405</t>
+          <t>CIN7401</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>04342A</t>
+          <t>04342C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Projeto de Informatização</t>
+          <t>Estudos Métricos da Informação</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2379,39 +2379,39 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>5.1010-2</t>
+          <t>3.1830-4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>CED-103 C</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Flavio Augusto Carraro</t>
+          <t>Adilson Luiz Pinto</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CIN7405</t>
+          <t>CIN7402</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>04342C</t>
+          <t>04342A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Projeto de Informatização</t>
+          <t>Editoração Científica</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2441,39 +2441,39 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4.2020-2</t>
+          <t>6.1010-2</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Flavio Augusto Carraro</t>
+          <t>Enrique Muriel Torrado</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CIN7406</t>
+          <t>CIN7402</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>04342A</t>
+          <t>04342C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Preservação Digital</t>
+          <t>Editoração Científica</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6.0820-2</t>
+          <t>6.1830-2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>CED-103 C</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2520,22 +2520,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CIN7406</t>
+          <t>CIN7403</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>04342C</t>
+          <t>04342B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Preservação Digital</t>
+          <t>Acessibilidade e Inclusão Digital</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2565,44 +2565,44 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2.2020-2</t>
+          <t>4.1620-2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>CED-004 D</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>Ilson Wilmar Rodrigues Filho</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CIN7412</t>
+          <t>CIN7404</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>02342C</t>
+          <t>04342A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Marketing da Informação</t>
+          <t>Planejamento Estratégico</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2ª Fase</t>
+          <t>4ª Fase</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2622,49 +2622,49 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5.2020-2</t>
+          <t>4.0820-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>Rogerio da Silva Nunes</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CIN7412</t>
+          <t>CIN7404</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>04342A</t>
+          <t>04342C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Marketing da Informação</t>
+          <t>Planejamento Estratégico</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2ª Fase</t>
+          <t>4ª Fase</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2684,49 +2684,49 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>3.1010-2</t>
+          <t>6.2020-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>CED-004 D</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Sonali Paula Molin Bedin</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CIN7501</t>
+          <t>CIN7405</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>05342</t>
+          <t>04342A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Arquitetura da Informação e Usabilidade</t>
+          <t>Projeto de Informatização</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5ª Fase</t>
+          <t>4ª Fase</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2746,49 +2746,49 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2.1830-2</t>
+          <t>5.1010-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Márcio Matias</t>
+          <t>Gustavo Medeiros de Araújo</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CIN7502</t>
+          <t>CIN7405</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>05342</t>
+          <t>04342C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mineração de Texto</t>
+          <t>Projeto de Informatização</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>5ª Fase</t>
+          <t>4ª Fase</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2808,49 +2808,49 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>5.2020-2</t>
+          <t>4.2020-2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Flavio Augusto Carraro</t>
+          <t>Gustavo Medeiros de Araújo</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CIN7503</t>
+          <t>CIN7406</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>05342</t>
+          <t>04342A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Bancos de Dados</t>
+          <t>Preservação Digital</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>5ª Fase</t>
+          <t>4ª Fase</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2870,49 +2870,49 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6.2020-2</t>
+          <t>6.0820-2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Flavio Augusto Carraro</t>
+          <t>Camila Schwinden Lehmkuhl</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CIN7504</t>
+          <t>CIN7406</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>05342</t>
+          <t>04342C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Gerenciamento de Projetos</t>
+          <t>Preservação Digital</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5ª Fase</t>
+          <t>4ª Fase</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2932,17 +2932,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>6.1830-2</t>
+          <t>2.2020-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2954,27 +2954,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CIN7505</t>
+          <t>CIN7412</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>05342</t>
+          <t>04342A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Estágio em Ciência da Informação</t>
+          <t>Marketing da Informação</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>5ª Fase</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2984,59 +2984,59 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2.1420-2</t>
+          <t>3.1010-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>CED-105 B</t>
+          <t>CED-004 D</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Nathalia Berger Werlang</t>
+          <t>Sonali Paula Molin Bedin</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CIN7601</t>
+          <t>CIN7412</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>06342</t>
+          <t>04342C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Linked Data</t>
+          <t>Marketing da Informação</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6ª Fase</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3056,49 +3056,49 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>4.1830-2</t>
+          <t>5.2020-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>EF1-EFI301</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Flavio Augusto Carraro</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CIN7602</t>
+          <t>CIN7501</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>06342</t>
+          <t>05342</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mídias Sociais</t>
+          <t>Arquitetura da Informação e Usabilidade</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6ª Fase</t>
+          <t>5ª Fase</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3123,44 +3123,44 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>6.1830-2</t>
+          <t>2.2020-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-516B</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Flavio Augusto Carraro</t>
+          <t>Márcio Matias</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CIN7603</t>
+          <t>CIN7502</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>06342</t>
+          <t>05342</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Empreendedorismo II</t>
+          <t>Mineração de Texto</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6ª Fase</t>
+          <t>5ª Fase</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3175,54 +3175,54 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2.1830-4</t>
+          <t>3.2020-2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE129</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Nathalia Berger Werlang</t>
+          <t>Flavio Augusto Carraro</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CIN7604</t>
+          <t>CIN7503</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>06342</t>
+          <t>05342</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TCC</t>
+          <t>Bancos de Dados</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6ª Fase</t>
+          <t>5ª Fase</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3237,59 +3237,59 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4.1620-2</t>
+          <t>6.2020-2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE131</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Márcio Matias</t>
+          <t>Flavio Augusto Carraro</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CIN7903</t>
+          <t>CIN7504</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>06342</t>
+          <t>05342</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Inteligência Competitiva</t>
+          <t>Gerenciamento de Projetos</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>5ª Fase (Optativa)</t>
+          <t>5ª Fase</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>Obrigatória</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3304,121 +3304,121 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3.1830-2</t>
+          <t>6.1830-2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE129</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>A contratar</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CIN7904</t>
+          <t>CIN7505</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>06342</t>
+          <t>05342</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Avaliação de Desempenho</t>
+          <t>Estágio em Ciência da Informação</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5ª Fase (Optativa)</t>
+          <t>5ª Fase</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>Obrigatória</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>432</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>5.1830-2</t>
+          <t>2.1420-2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-105 B</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>Nathalia Berger Werlang</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CIN7905</t>
+          <t>CIN7601</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>05342</t>
+          <t>06342</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Teoria da Decisão</t>
+          <t>Linked Data</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6ª Fase (Optativa)</t>
+          <t>6ª Fase</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>Obrigatória</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3438,39 +3438,39 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE131</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>Flavio Augusto Carraro</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CIN7907</t>
+          <t>CIN7602</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>02342</t>
+          <t>06342</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Lógica Aplicada I</t>
+          <t>Mídias Sociais</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2ª Fase</t>
+          <t>6ª Fase</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3485,22 +3485,22 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>3.1830-4</t>
+          <t>6.1830-2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE131</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3512,89 +3512,89 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CIN7917</t>
+          <t>CIN7603</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>05342</t>
+          <t>06342</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Visualização da Informação</t>
+          <t>Empreendedorismo II</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5ª Fase (Optativa)</t>
+          <t>6ª Fase</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>Obrigatória</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>4.1830-2</t>
+          <t>2.1830-4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE129</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Márcio Matias</t>
+          <t>Nathalia Berger Werlang</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CIN7925</t>
+          <t>CIN7604</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>01342</t>
+          <t>06342</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Introdução a Algoritmos</t>
+          <t>TCC</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1ª Fase</t>
+          <t>6ª Fase</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3604,44 +3604,44 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>5.2020-2</t>
+          <t>4.1620-2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>EF1-EFI303</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Ricardo Alexandre Reinaldo de Moraes</t>
+          <t>Márcio Matias</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CIN7927</t>
+          <t>CIN7904</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3651,19 +3651,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Gestão da Informação Pública</t>
+          <t>Avaliação de Desempenho</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>5ª Fase (Optativa)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>Optativa</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Optativa</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>Comum</t>
@@ -3676,49 +3676,49 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2.1830-2</t>
+          <t>4.1830-2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE129</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>A contratar</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CIN7935</t>
+          <t>CIN7906</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>06342</t>
+          <t>05342</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Liderança e Gerência</t>
+          <t>Inovação e Informação</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>6ª Fase (Optativa)</t>
+          <t>5ª Fase (Optativa)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3733,54 +3733,54 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>5.1830-2</t>
+          <t>3.1830-2 | 5.1830-2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>CED-LBCON</t>
+          <t>CCE-CCE129 | CCE-CCE129</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Sonali Paula Molin Bedin</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CIN7936</t>
+          <t>CIN7907</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>03342A</t>
+          <t>02342</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Proteção de Dados Pessoais</t>
+          <t>Lógica Aplicada I</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>3ª Fase</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3790,64 +3790,64 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2.0820-2</t>
+          <t>5.1830-4</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>CCE-CCE131</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Marcelo Minghelli</t>
+          <t>Ricardo Alexandre Reinaldo de Moraes e Flavio Augusto Carraro</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CIN7936</t>
+          <t>CIN7913</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>03342C</t>
+          <t>04342</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Proteção de Dados Pessoais</t>
+          <t>Lógica Instrumental II</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>3ª Fase</t>
+          <t>5ª Fase (Optativa)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Obrigatória</t>
+          <t>Optativa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3862,49 +3862,49 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>3.1830-2</t>
+          <t>4.1420-2</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>CED-102 C</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Marcelo Minghelli</t>
+          <t>Ilson Wilmar Rodrigues Filho</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CIN7938</t>
+          <t>CIN7917</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>05342</t>
+          <t>06342</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Segurança da Informação</t>
+          <t>Visualização da Informação</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>5ª Fase (Optativa)</t>
+          <t>6ª Fase (Optativa)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3924,59 +3924,59 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>3.2020-2</t>
+          <t>4.1830-2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-516B</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>A contratar</t>
+          <t>Márcio Matias</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CIN7943</t>
+          <t>CIN7919</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>01342</t>
+          <t>05342</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Experiência do Usuário (UX) User Experience</t>
+          <t>Informação, Direito e Cidadania</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1ª Fase</t>
+          <t>5ª Fase (Optativa)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Obrigatória</t>
+          <t>Optativa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3996,49 +3996,49 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-516B</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Márcio Matias</t>
+          <t>Luis Roberto Sousa Mendes</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CIN7945</t>
+          <t>CIN7925</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>05342</t>
+          <t>01342</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Fontes de Informação Tecnológica</t>
+          <t>Introdução a Algoritmos</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>5ª Fase (Optativa)</t>
+          <t>1ª Fase</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>Obrigatória</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4048,49 +4048,49 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2.2020-2</t>
+          <t>4.1830-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE131</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Márcio Matias</t>
+          <t>Flavio Augusto Carraro</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CIN7946</t>
+          <t>CIN7935</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>05342</t>
+          <t>06342</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Pitch de Carreira</t>
+          <t>Liderança e Gerência</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>6ª Fase (Optativa)</t>
+          <t>5ª Fase (Optativa)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4110,34 +4110,34 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>5.2020-2</t>
+          <t>2.1830-2</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>CED-LBCON</t>
+          <t>CCE-CCE131</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Sonali Paula Molin Bedin</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HST7921</t>
+          <t>CIN7936</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>História do Brasil Contemporâneo</t>
+          <t>Proteção de Dados Pessoais</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>5.0820-4</t>
+          <t>2.0820-2</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4187,19 +4187,19 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Roselane Neckel</t>
+          <t>Marcelo Minghelli</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HST7921</t>
+          <t>CIN7936</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>História do Brasil Contemporâneo</t>
+          <t>Proteção de Dados Pessoais</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4239,44 +4239,44 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>6.1830-4</t>
+          <t>4.2020-2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>CED-102 C</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Roselane Neckel</t>
+          <t>Marcelo Minghelli</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>INE5111</t>
+          <t>CIN7943</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>02342A</t>
+          <t>01342</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Estatística Aplicada I</t>
+          <t>Experiência do Usuário (UX) User Experience</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2ª Fase</t>
+          <t>1ª Fase</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4286,183 +4286,183 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>3.0820-2 | 4.1010-2</t>
+          <t>4.2020-2</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>CED-LBPREV | CED-LBPREV</t>
+          <t>CCE-CCE131</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Vera do Carmo Comparsi de Vargas</t>
+          <t>Márcio Matias</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>INE5111</t>
+          <t>CIN7944</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>02342C</t>
+          <t>06342</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Estatística Aplicada I</t>
+          <t>Curadoria Digital</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2ª Fase</t>
+          <t>6ª Fase (Optativa)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Obrigatória</t>
+          <t>Optativa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2.1830-2 | 5.1830-2</t>
+          <t>4.2020-2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>CED-LBPREV | CED-102 C</t>
+          <t>CCE-CCE129</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Manoella Reis Cardenuto</t>
+          <t>Flavio Augusto Carraro</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LLV7802</t>
+          <t>CIN7945</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>01342C</t>
+          <t>05342</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Leitura e Produção do Texto</t>
+          <t>Fontes de Informação Tecnológica</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1ª Fase</t>
+          <t>Optativa</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Obrigatória</t>
+          <t>Optativa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>6.1830-4</t>
+          <t>2.1830-2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-516B</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Gabriela Rempel</t>
+          <t>Márcio Matias</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LLV7802</t>
+          <t>HST7921</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>01342D</t>
+          <t>03342A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Leitura e Produção do Texto</t>
+          <t>História do Brasil Contemporâneo</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1ª Fase</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4487,79 +4487,389 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>6.1830-4</t>
+          <t>5.0820-4</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Silvia Ines Coneglian Carrilho de Vasconcelos</t>
+          <t>Roselane Neckel</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026.2</t>
+          <t>2026.1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>HST7921</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>03342C</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>História do Brasil Contemporâneo</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>3ª Fase</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Obrigatória</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Comum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>6.1830-4</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>CFH-1FH322</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Roselane Neckel</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>INE5111</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>04342A</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Estatística Aplicada I</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2ª Fase</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Obrigatória</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Comum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>3.0820-2 | 4.1010-2</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>CED-LBPREV | CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Vera do Carmo Comparsi de Vargas</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>INE5111</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>04342C</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Estatística Aplicada I</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2ª Fase</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Obrigatória</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Comum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2.1830-2 | 5.1830-2</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>CTC-CTC106 | CTC-CTC106</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Manoella Reis Cardenuto</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>LLV7802</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>01342C</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Leitura e Produção do Texto</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1ª Fase</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Obrigatória</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Comum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>6.1830-4</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>EF1-EFI304</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Graziela Hahn</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>LLV7802</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>01342D</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Leitura e Produção do Texto</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1ª Fase</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Obrigatória</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Comum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>6.1830-4</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>EF1-EFI304</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Graziela Hahn</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026.1</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>MTM3110</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>01342</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Cálculo</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>1ª Fase</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Obrigatória</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Específico</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>3.1830-2 | 5.1830-2</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>AUX-ALOCAR | AUX-ALOCAR</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Francisco Carlos Caramello Junior</t>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>EF1-EFI405 | EF1-EFI405</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Camilo Campana e Camila Aparecida Benedito Rodrigues de Lima</t>
         </is>
       </c>
     </row>
@@ -4574,14 +4884,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="63" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4849,7 +5159,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7144 (01342)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4864,7 +5174,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CIN7144 (01342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4881,7 +5191,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7145 (01342)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4896,7 +5206,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CIN7145 (01342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4913,7 +5223,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7145 (01342)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4928,7 +5238,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CIN7145 (01342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4945,7 +5255,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CAD5103 (01342C) / CAD5103 (01342D)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4955,7 +5265,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CIN7141 (01342C)</t>
+          <t>CIN7925 (01342)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4977,7 +5287,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CAD5103 (01342C) / CAD5103 (01342D)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4987,7 +5297,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CIN7141 (01342C)</t>
+          <t>CIN7925 (01342)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5009,7 +5319,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CAD5103 (01342C) / CAD5103 (01342D)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5024,7 +5334,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CIN7925 (01342)</t>
+          <t>CIN7141 (01342C)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -5041,7 +5351,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CAD5103 (01342C) / CAD5103 (01342D)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5056,7 +5366,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CIN7925 (01342)</t>
+          <t>CIN7141 (01342C)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5099,242 +5409,198 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CAD5103 (01342C)</t>
+          <t>CIN7141 (01342C)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Administração I</t>
+          <t>Lógica Instrumental I</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE129</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Monica Scoz Mendes</t>
+          <t>Ilson Wilmar Rodrigues Filho</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CAD5103 (01342D)</t>
+          <t>CIN7143 (01342C)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Administração I</t>
+          <t>Empreendedorismo I</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>EF1-EFI402</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CIN7141 (01342C)</t>
+          <t>CIN7144 (01342)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lógica Instrumental I</t>
+          <t>Tutoria Acadêmica I</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ilson Wilmar Rodrigues Filho</t>
+          <t>Ricardo Alexandre Reinaldo de Moraes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CIN7143 (01342C)</t>
+          <t>CIN7145 (01342)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Empreendedorismo I</t>
+          <t>Gestão da Informação</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-103 C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>Nathalia Berger Werlang</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CIN7144 (01342)</t>
+          <t>CIN7925 (01342)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tutoria Acadêmica I</t>
+          <t>Introdução a Algoritmos</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE131</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ricardo Alexandre Reinaldo de Moraes</t>
+          <t>Flavio Augusto Carraro</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CIN7145 (01342)</t>
+          <t>CIN7943 (01342)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gestão da Informação</t>
+          <t>Experiência do Usuário (UX) User Experience</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE131</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nathalia Berger Werlang</t>
+          <t>Márcio Matias</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CIN7925 (01342)</t>
+          <t>LLV7802 (01342C)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Introdução a Algoritmos</t>
+          <t>Leitura e Produção do Texto</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>EF1-EFI304</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ricardo Alexandre Reinaldo de Moraes</t>
+          <t>Graziela Hahn</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CIN7943 (01342)</t>
+          <t>LLV7802 (01342D)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Experiência do Usuário (UX) User Experience</t>
+          <t>Leitura e Produção do Texto</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>EF1-EFI304</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Márcio Matias</t>
+          <t>Graziela Hahn</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LLV7802 (01342C)</t>
+          <t>MTM3110 (01342)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Leitura e Produção do Texto</t>
+          <t>Cálculo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>EF1-EFI405 | EF1-EFI405</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Gabriela Rempel</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>LLV7802 (01342D)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Leitura e Produção do Texto</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AUX-ALOCAR</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Silvia Ines Coneglian Carrilho de Vasconcelos</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>MTM3110 (01342)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Cálculo</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AUX-ALOCAR | AUX-ALOCAR</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Francisco Carlos Caramello Junior</t>
+          <t>Camilo Campana e Camila Aparecida Benedito Rodrigues de Lima</t>
         </is>
       </c>
     </row>
@@ -5353,14 +5619,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -5419,7 +5685,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7203 (02342A)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -5436,12 +5702,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7206 (02342A)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INE5111 (02342A)</t>
+          <t>CIN7202 (02342A) / INE5111 (04342A)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5451,12 +5717,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7203 (02342A)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7201 (02342A)</t>
         </is>
       </c>
     </row>
@@ -5468,12 +5734,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7206 (02342A)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INE5111 (02342A)</t>
+          <t>CIN7202 (02342A) / INE5111 (04342A)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5488,7 +5754,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7201 (02342A)</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5771,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CIN7412 (04342A)</t>
+          <t>CIN7206 (02342A) / CIN7412 (04342A)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>INE5111 (02342A)</t>
+          <t>INE5111 (04342A)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5520,7 +5786,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7201 (02342A)</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5803,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CIN7412 (04342A)</t>
+          <t>CIN7206 (02342A) / CIN7412 (04342A)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>INE5111 (02342A)</t>
+          <t>INE5111 (04342A)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5552,7 +5818,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7201 (02342A)</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5862,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7205 (02342B)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5628,7 +5894,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7205 (02342B)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5660,7 +5926,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7205 (02342B)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5692,7 +5958,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7205 (02342B)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5702,12 +5968,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7204 (02342C)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CIN7204 (02342C)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5724,22 +5990,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INE5111 (02342C)</t>
+          <t>INE5111 (04342C)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CIN7907 (02342)</t>
+          <t>CIN7206 (02342C)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7203 (02342C)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>INE5111 (02342C)</t>
+          <t>CIN7907 (02342) / INE5111 (04342C)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -5756,22 +6022,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INE5111 (02342C)</t>
+          <t>INE5111 (04342C)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CIN7907 (02342)</t>
+          <t>CIN7206 (02342C)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7203 (02342C)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>INE5111 (02342C)</t>
+          <t>CIN7907 (02342) / INE5111 (04342C)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -5793,17 +6059,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CIN7907 (02342)</t>
+          <t>CIN7206 (02342C)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7202 (02342C)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CIN7412 (02342C)</t>
+          <t>CIN7412 (04342C) / CIN7907 (02342)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -5825,17 +6091,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CIN7907 (02342)</t>
+          <t>CIN7206 (02342C)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7202 (02342C)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CIN7412 (02342C)</t>
+          <t>CIN7412 (04342C) / CIN7907 (02342)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5878,7 +6144,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CIN7201 (02342C)</t>
+          <t>CIN7201 (02342A)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5888,7 +6154,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-004 D</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5900,130 +6166,306 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CIN7204 (02342C)</t>
+          <t>CIN7201 (02342C)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tutoria Acadêmica II</t>
+          <t>Sistemas de Organização do Conhecimento</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CED-D109</t>
+          <t>EF1-EFI405</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ricardo Alexandre Reinaldo de Moraes</t>
+          <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CIN7412 (02342C)</t>
+          <t>CIN7202 (02342A)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Marketing da Informação</t>
+          <t>Sociedade da Informação</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>Enrique Muriel Torrado</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CIN7412 (04342A)</t>
+          <t>CIN7202 (02342C)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Marketing da Informação</t>
+          <t>Sociedade da Informação</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CED-004 D</t>
+          <t>EF1-EFI305</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sonali Paula Molin Bedin</t>
+          <t>Enrique Muriel Torrado</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CIN7907 (02342)</t>
+          <t>CIN7203 (02342A)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lógica Aplicada I</t>
+          <t>Ética Profissional</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-004 D</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Flavio Augusto Carraro</t>
+          <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>INE5111 (02342A)</t>
+          <t>CIN7203 (02342C)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Estatística Aplicada I</t>
+          <t>Ética Profissional</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CED-LBPREV | CED-LBPREV</t>
+          <t>EF1-EFI304</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Vera do Carmo Comparsi de Vargas</t>
+          <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>INE5111 (02342C)</t>
+          <t>CIN7204 (02342C)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>Tutoria Acadêmica II</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CED-105 B</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ricardo Alexandre Reinaldo de Moraes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CIN7205 (02342B)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Recuperação da Informação</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CCE-516B</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CIN7206 (02342A)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fontes Gerais de Informação</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CED-102 C | CED-102 C</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Aline Carmes Krüger</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CIN7206 (02342C)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fontes Gerais de Informação</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Patricia da Silva Neubert</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CIN7412 (04342A)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Marketing da Informação</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CED-004 D</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Sonali Paula Molin Bedin</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CIN7412 (04342C)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Marketing da Informação</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EF1-EFI301</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sabrina Borges Ramos de Carvalho</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CIN7907 (02342)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Lógica Aplicada I</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CCE-CCE131</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Ricardo Alexandre Reinaldo de Moraes e Flavio Augusto Carraro</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>INE5111 (04342A)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>Estatística Aplicada I</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CED-LBPREV | CED-102 C</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CED-LBPREV | CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Vera do Carmo Comparsi de Vargas</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>INE5111 (04342C)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Estatística Aplicada I</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CTC-CTC106 | CTC-CTC106</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Manoella Reis Cardenuto</t>
         </is>
@@ -6049,8 +6491,8 @@
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
@@ -6132,12 +6574,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>CIN7301 (03342A)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>CIN7304 (03342A)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CIN7309 (03342A)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -6164,12 +6606,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>CIN7301 (03342A)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>CIN7304 (03342A)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CIN7309 (03342A)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6196,7 +6638,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CIN7301 (03342A)</t>
+          <t>CIN7309 (03342A)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6228,7 +6670,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CIN7301 (03342A)</t>
+          <t>CIN7309 (03342A)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -6420,17 +6862,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CIN7936 (03342C)</t>
+          <t>CIN7309 (03342C)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CIN7309 (02342C)</t>
+          <t>CIN7309 (03342C)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CIN7302 (03342C)</t>
+          <t>CIN7301 (03342C)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -6452,17 +6894,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CIN7936 (03342C)</t>
+          <t>CIN7309 (03342C)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CIN7309 (02342C)</t>
+          <t>CIN7309 (03342C)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CIN7302 (03342C)</t>
+          <t>CIN7301 (03342C)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -6484,12 +6926,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CIN7301 (03342C)</t>
+          <t>CIN7302 (03342C)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CIN7309 (02342C)</t>
+          <t>CIN7936 (03342C)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6516,12 +6958,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CIN7301 (03342C)</t>
+          <t>CIN7302 (03342C)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CIN7309 (02342C)</t>
+          <t>CIN7936 (03342C)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6579,7 +7021,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CFH-1FH330</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6601,12 +7043,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>EF1-EFI304</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
         </is>
       </c>
     </row>
@@ -6628,7 +7070,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Maria Zanela</t>
+          <t>Elizete Vieira Vitorino e Maria Zanela</t>
         </is>
       </c>
     </row>
@@ -6645,12 +7087,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>EF1-EFI401</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Edgar Bisset Alvarez</t>
+          <t>Mariana Xavier de Oliveira</t>
         </is>
       </c>
     </row>
@@ -6694,7 +7136,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Maria Zanela</t>
+          <t>Maria Zanela e Elizete Vieira Vitorino</t>
         </is>
       </c>
     </row>
@@ -6711,7 +7153,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -6760,7 +7202,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Maria Zanela</t>
+          <t>Maria Zanela e Elizete Vieira Vitorino</t>
         </is>
       </c>
     </row>
@@ -6782,14 +7224,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Maria Zanela</t>
+          <t>Maria Zanela e Elizete Vieira Vitorino</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CIN7309 (02342C)</t>
+          <t>CIN7309 (03342A)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6799,19 +7241,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>CED-LBTEC | CED-LBTEC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Rogerio da Silva Nunes</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CIN7309 (03342A)</t>
+          <t>CIN7309 (03342C)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6821,12 +7263,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>CED-LBTEC | CED-LBTEC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Rogerio da Silva Nunes</t>
         </is>
       </c>
     </row>
@@ -6909,7 +7351,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>CFH-1FH322</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6938,7 +7380,7 @@
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
@@ -6994,7 +7436,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CIN7404 (04342A)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7004,7 +7446,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CIN7404 (04342A)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7468,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7404 (04342A)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7058,7 +7500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7404 (04342A)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -7250,7 +7692,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7403 (04342B)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -7272,7 +7714,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CIN7403 (04342C)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7282,7 +7724,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CIN7403 (04342C)</t>
+          <t>CIN7403 (04342B)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -7546,7 +7988,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CIN7403 (04342C)</t>
+          <t>CIN7403 (04342B)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7556,7 +7998,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CED-LBPREV | CED-LBPREV</t>
+          <t>CED-004 D</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -7578,12 +8020,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CED-103 C | CED-103 C</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Maria Zanela</t>
+          <t>Rogerio da Silva Nunes</t>
         </is>
       </c>
     </row>
@@ -7627,7 +8069,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Flavio Augusto Carraro</t>
+          <t>Gustavo Medeiros de Araújo</t>
         </is>
       </c>
     </row>
@@ -7644,12 +8086,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Flavio Augusto Carraro</t>
+          <t>Gustavo Medeiros de Araújo</t>
         </is>
       </c>
     </row>
@@ -7671,7 +8113,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Enrique Muriel Torrado</t>
+          <t>Camila Schwinden Lehmkuhl</t>
         </is>
       </c>
     </row>
@@ -7717,7 +8159,7 @@
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -7965,7 +8407,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7913 (04342)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7997,7 +8439,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7913 (04342)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8083,22 +8525,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CIN7501 (05342)</t>
+          <t>CIN7935 (06342)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CIN7903 (06342)</t>
+          <t>CIN7906 (05342)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CIN7917 (05342)</t>
+          <t>CIN7904 (05342)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CIN7904 (06342)</t>
+          <t>CIN7906 (05342)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -8115,22 +8557,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CIN7501 (05342)</t>
+          <t>CIN7935 (06342)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CIN7903 (06342)</t>
+          <t>CIN7906 (05342)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CIN7917 (05342)</t>
+          <t>CIN7904 (05342)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CIN7904 (06342)</t>
+          <t>CIN7906 (05342)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -8147,22 +8589,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CIN7945 (05342)</t>
+          <t>CIN7501 (05342)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CIN7938 (05342)</t>
+          <t>CIN7502 (05342)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7919 (05342)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CIN7502 (05342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -8179,22 +8621,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CIN7945 (05342)</t>
+          <t>CIN7501 (05342)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CIN7938 (05342)</t>
+          <t>CIN7502 (05342)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7919 (05342)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CIN7502 (05342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -8247,7 +8689,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-516B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -8269,7 +8711,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE129</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -8291,7 +8733,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE131</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -8313,7 +8755,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE129</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -8347,17 +8789,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CIN7903 (06342)</t>
+          <t>CIN7904 (05342)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Inteligência Competitiva</t>
+          <t>Avaliação de Desempenho</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE129</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -8369,17 +8811,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CIN7904 (06342)</t>
+          <t>CIN7906 (05342)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Avaliação de Desempenho</t>
+          <t>Inovação e Informação</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE129 | CCE-CCE129</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -8391,66 +8833,66 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CIN7917 (05342)</t>
+          <t>CIN7913 (04342)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Visualização da Informação</t>
+          <t>Lógica Instrumental II</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Márcio Matias</t>
+          <t>Ilson Wilmar Rodrigues Filho</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CIN7938 (05342)</t>
+          <t>CIN7919 (05342)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Segurança da Informação</t>
+          <t>Informação, Direito e Cidadania</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-516B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Luis Roberto Sousa Mendes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CIN7945 (05342)</t>
+          <t>CIN7935 (06342)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fontes de Informação Tecnológica</t>
+          <t>Liderança e Gerência</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE131</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Márcio Matias</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
@@ -8469,14 +8911,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -8845,17 +9287,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CIN7905 (05342)</t>
+          <t>CIN7601 (06342)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CIN7601 (06342)</t>
+          <t>CIN7917 (06342)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CIN7935 (06342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -8877,17 +9319,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CIN7905 (05342)</t>
+          <t>CIN7601 (06342)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CIN7601 (06342)</t>
+          <t>CIN7917 (06342)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CIN7935 (06342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -8914,12 +9356,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7944 (06342)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CIN7946 (05342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -8946,12 +9388,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7944 (06342)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CIN7946 (05342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -9004,7 +9446,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE131</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -9026,7 +9468,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE131</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -9048,7 +9490,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-CCE129</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -9070,7 +9512,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>EF1-EFI303</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -9082,66 +9524,44 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CIN7905 (05342)</t>
+          <t>CIN7917 (06342)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Teoria da Decisão</t>
+          <t>Visualização da Informação</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CCE-516B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>Márcio Matias</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CIN7935 (06342)</t>
+          <t>CIN7944 (06342)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Liderança e Gerência</t>
+          <t>Curadoria Digital</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CED-LBCON</t>
+          <t>CCE-CCE129</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sonali Paula Molin Bedin</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CIN7946 (05342)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Pitch de Carreira</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CED-LBCON</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Sonali Paula Molin Bedin</t>
+          <t>Flavio Augusto Carraro</t>
         </is>
       </c>
     </row>

--- a/resultados/relatorio_final.xlsx
+++ b/resultados/relatorio_final.xlsx
@@ -179,8 +179,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Legenda_Fase_6" displayName="Legenda_Fase_6" ref="A19:D25" headerRowCount="1">
-  <autoFilter ref="A19:D25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Legenda_Fase_6" displayName="Legenda_Fase_6" ref="A19:D26" headerRowCount="1">
+  <autoFilter ref="A19:D26"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Legenda_Fase_1" displayName="Legenda_Fase_1" ref="A19:D28" headerRowCount="1">
-  <autoFilter ref="A19:D28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Legenda_Fase_1" displayName="Legenda_Fase_1" ref="A19:D30" headerRowCount="1">
+  <autoFilter ref="A19:D30"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
@@ -220,8 +220,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Legenda_Fase_2" displayName="Legenda_Fase_2" ref="A19:D34" headerRowCount="1">
-  <autoFilter ref="A19:D34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Legenda_Fase_2" displayName="Legenda_Fase_2" ref="A19:D26" headerRowCount="1">
+  <autoFilter ref="A19:D26"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -660,12 +660,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CIN7141</t>
+          <t>CAD5103</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lógica Instrumental I</t>
+          <t>Administração I</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -695,49 +695,49 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.2020-2</t>
+          <t>2.1830-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>CCE-CCE129</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Ilson Wilmar Rodrigues Filho</t>
+          <t>Monica Scoz Mendes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CIN7143</t>
+          <t>CAD5103</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>01342C</t>
+          <t>01342D</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Empreendedorismo I</t>
+          <t>Administração I</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,49 +757,49 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.2020-2</t>
+          <t>2.1830-4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>EF1-EFI402</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>A contratar</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CIN7144</t>
+          <t>CIN7141</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>01342</t>
+          <t>01342C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tutoria Acadêmica I</t>
+          <t>Lógica Instrumental I</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -819,49 +819,49 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.1510-1</t>
+          <t>4.1830-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Ricardo Alexandre Reinaldo de Moraes</t>
+          <t>Ilson Wilmar Rodrigues Filho</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CIN7145</t>
+          <t>CIN7143</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>01342</t>
+          <t>01342C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gestão da Informação</t>
+          <t>Empreendedorismo I</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -886,49 +886,49 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.1620-2</t>
+          <t>3.2020-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>CED-103 C</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Nathalia Berger Werlang</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CIN7201</t>
+          <t>CIN7144</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>02342A</t>
+          <t>01342</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sistemas de Organização do Conhecimento</t>
+          <t>Tutoria Acadêmica I</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2ª Fase</t>
+          <t>1ª Fase</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -943,54 +943,54 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.0820-4</t>
+          <t>5.1510-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>CED-004 D</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Mariana Xavier de Oliveira</t>
+          <t>Ricardo Alexandre Reinaldo de Moraes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CIN7201</t>
+          <t>CIN7145</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>02342C</t>
+          <t>01342</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sistemas de Organização do Conhecimento</t>
+          <t>Gestão da Informação</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2ª Fase</t>
+          <t>1ª Fase</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1000,54 +1000,54 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.1830-4</t>
+          <t>5.1620-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>EF1-EFI405</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
+          <t>Nathalia Berger Werlang</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CIN7202</t>
+          <t>CIN7201</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>02342A</t>
+          <t>02342C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sociedade da Informação</t>
+          <t>Sistemas de Organização do Conhecimento</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1067,39 +1067,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.0820-2</t>
+          <t>6.1830-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Enrique Muriel Torrado</t>
+          <t>Mariana Xavier de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CIN7202</t>
+          <t>CIN7204</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sociedade da Informação</t>
+          <t>Tutoria Acadêmica II</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1129,54 +1129,54 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.2020-2</t>
+          <t>5.1710-1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>EF1-EFI305</t>
+          <t>CED-D109</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Enrique Muriel Torrado</t>
+          <t>Ricardo Alexandre Reinaldo de Moraes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CIN7203</t>
+          <t>CIN7301</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>02342A</t>
+          <t>03342A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ética Profissional</t>
+          <t>Introdução à Representação Temática</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2ª Fase</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1201,44 +1201,44 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.0730-2</t>
+          <t>3.1010-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>CED-004 D</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
+          <t>Mariana Xavier de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CIN7203</t>
+          <t>CIN7301</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>02342C</t>
+          <t>03342C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ética Profissional</t>
+          <t>Introdução à Representação Temática</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2ª Fase</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1263,44 +1263,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.1830-2</t>
+          <t>3.2020-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>EF1-EFI304</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
+          <t>A contratar</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CIN7204</t>
+          <t>CIN7302</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>02342C</t>
+          <t>03342A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tutoria Acadêmica II</t>
+          <t>Introdução à Representação Descritiva</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2ª Fase</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1315,54 +1315,54 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.1710-1</t>
+          <t>6.1010-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>CED-105 B</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ricardo Alexandre Reinaldo de Moraes</t>
+          <t>Maria Zanela</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CIN7205</t>
+          <t>CIN7302</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>02342B</t>
+          <t>03342C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Recuperação da Informação</t>
+          <t>Introdução à Representação Descritiva</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2ª Fase</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1377,54 +1377,54 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.1420-4</t>
+          <t>5.1830-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>CCE-516B</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>A contratar</t>
+          <t>Edgar Bisset Alvarez</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CIN7206</t>
+          <t>CIN7303</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>02342A</t>
+          <t>03342A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Fontes Gerais de Informação</t>
+          <t>Metodologia da Pesquisa</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2ª Fase</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1449,44 +1449,44 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.0820-2 | 3.1010-2</t>
+          <t>2.1010-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>CED-102 C | CED-102 C</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Aline Carmes Krüger</t>
+          <t>Luis Roberto Sousa Mendes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CIN7206</t>
+          <t>CIN7303</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>02342C</t>
+          <t>03342C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fontes Gerais de Informação</t>
+          <t>Metodologia da Pesquisa</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2ª Fase</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1511,29 +1511,29 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.1830-4</t>
+          <t>2.2020-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>CED-103 C</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Patricia da Silva Neubert</t>
+          <t>Maria Zanela</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CIN7301</t>
+          <t>CIN7304</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Introdução à Representação Temática</t>
+          <t>Introdução à Bancos de Dados</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1578,24 +1578,24 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>CFH-1FH330</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Mariana Xavier de Oliveira</t>
+          <t>Gustavo Medeiros de Araújo</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CIN7301</t>
+          <t>CIN7304</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Introdução à Representação Temática</t>
+          <t>Introdução à Bancos de Dados</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1635,29 +1635,29 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5.1830-2</t>
+          <t>5.2020-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>EF1-EFI304</t>
+          <t>CED-102 C</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
+          <t>Gustavo Medeiros de Araújo</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CIN7302</t>
+          <t>CIN7306</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Introdução à Representação Descritiva</t>
+          <t>Competência Informacional</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>6.1010-2</t>
+          <t>6.0820-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1707,19 +1707,19 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Elizete Vieira Vitorino e Maria Zanela</t>
+          <t>Maria Zanela</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CIN7302</t>
+          <t>CIN7306</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Introdução à Representação Descritiva</t>
+          <t>Competência Informacional</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1754,44 +1754,44 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3.2020-2</t>
+          <t>2.1830-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>EF1-EFI401</t>
+          <t>CED-103 C</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Mariana Xavier de Oliveira</t>
+          <t>Maria Zanela</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CIN7303</t>
+          <t>CIN7309</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>03342A</t>
+          <t>02342C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Metodologia da Pesquisa</t>
+          <t>Gestão de Processos Organizacionais</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1811,49 +1811,49 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.1010-2</t>
+          <t>4.1830-4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Luis Roberto Sousa Mendes</t>
+          <t>A contratar</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CIN7303</t>
+          <t>CIN7309</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>03342C</t>
+          <t>03342A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Metodologia da Pesquisa</t>
+          <t>Gestão de Processos Organizacionais</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1873,54 +1873,54 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.2020-2</t>
+          <t>4.0820-4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>CED-103 C</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Maria Zanela e Elizete Vieira Vitorino</t>
+          <t>A contratar</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CIN7304</t>
+          <t>CIN7401</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>03342A</t>
+          <t>04342A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Introdução à Bancos de Dados</t>
+          <t>Estudos Métricos da Informação</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3ª Fase</t>
+          <t>4ª Fase</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1945,44 +1945,44 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>4.0820-2</t>
+          <t>2.0820-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>CED-103 C</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Gustavo Medeiros de Araújo</t>
+          <t>Adilson Luiz Pinto</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CIN7304</t>
+          <t>CIN7401</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>03342C</t>
+          <t>04342C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Introdução à Bancos de Dados</t>
+          <t>Estudos Métricos da Informação</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3ª Fase</t>
+          <t>4ª Fase</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2007,44 +2007,44 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5.2020-2</t>
+          <t>3.1830-4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>CED-102 C</t>
+          <t>CED-103 C</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Gustavo Medeiros de Araújo</t>
+          <t>Adilson Luiz Pinto</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CIN7306</t>
+          <t>CIN7402</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>03342A</t>
+          <t>04342A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Competência Informacional</t>
+          <t>Editoração Científica</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3ª Fase</t>
+          <t>4ª Fase</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2069,44 +2069,44 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>6.0820-2</t>
+          <t>6.1010-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Maria Zanela e Elizete Vieira Vitorino</t>
+          <t>Enrique Muriel Torrado</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CIN7306</t>
+          <t>CIN7402</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>03342C</t>
+          <t>04342C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Competência Informacional</t>
+          <t>Editoração Científica</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3ª Fase</t>
+          <t>4ª Fase</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2.1830-2</t>
+          <t>6.1830-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2141,34 +2141,34 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Maria Zanela e Elizete Vieira Vitorino</t>
+          <t>Enrique Muriel Torrado</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CIN7309</t>
+          <t>CIN7403</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>03342A</t>
+          <t>04342C</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Gestão de Processos Organizacionais</t>
+          <t>Acessibilidade e Inclusão Digital</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3ª Fase</t>
+          <t>4ª Fase</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2183,54 +2183,54 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>3.1010-2 | 4.1010-2</t>
+          <t>2.1710-1 | 4.1710-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>CED-LBTEC | CED-LBTEC</t>
+          <t>CED-LBPREV | CED-LBPREV</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Rogerio da Silva Nunes</t>
+          <t>Ilson Wilmar Rodrigues Filho</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CIN7309</t>
+          <t>CIN7404</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>03342C</t>
+          <t>04342A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Gestão de Processos Organizacionais</t>
+          <t>Planejamento Estratégico</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3ª Fase</t>
+          <t>4ª Fase</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2255,39 +2255,39 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3.1830-2 | 4.1830-2</t>
+          <t>4.0730-1 | 6.0730-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>CED-LBTEC | CED-LBTEC</t>
+          <t>CED-103 C | CED-103 C</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Rogerio da Silva Nunes</t>
+          <t>Maria Zanela</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CIN7401</t>
+          <t>CIN7404</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>04342A</t>
+          <t>04342C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Estudos Métricos da Informação</t>
+          <t>Planejamento Estratégico</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2317,39 +2317,39 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2.0820-4</t>
+          <t>6.2020-2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>CED-103 C</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Adilson Luiz Pinto</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CIN7401</t>
+          <t>CIN7405</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>04342C</t>
+          <t>04342A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Estudos Métricos da Informação</t>
+          <t>Projeto de Informatização</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2379,39 +2379,39 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3.1830-4</t>
+          <t>5.1010-2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>CED-103 C</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Adilson Luiz Pinto</t>
+          <t>Flavio Augusto Carraro</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CIN7402</t>
+          <t>CIN7405</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>04342A</t>
+          <t>04342C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Editoração Científica</t>
+          <t>Projeto de Informatização</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2441,39 +2441,39 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6.1010-2</t>
+          <t>4.2020-2</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Enrique Muriel Torrado</t>
+          <t>Flavio Augusto Carraro</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CIN7402</t>
+          <t>CIN7406</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>04342C</t>
+          <t>04342A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Editoração Científica</t>
+          <t>Preservação Digital</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6.1830-2</t>
+          <t>6.0820-2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>CED-103 C</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2520,22 +2520,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CIN7403</t>
+          <t>CIN7406</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>04342B</t>
+          <t>04342C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Acessibilidade e Inclusão Digital</t>
+          <t>Preservação Digital</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2565,44 +2565,44 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>4.1620-2</t>
+          <t>2.2020-2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>CED-004 D</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Ilson Wilmar Rodrigues Filho</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CIN7404</t>
+          <t>CIN7412</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>04342A</t>
+          <t>02342C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Planejamento Estratégico</t>
+          <t>Marketing da Informação</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4ª Fase</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2622,49 +2622,49 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4.0820-2</t>
+          <t>5.2020-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Rogerio da Silva Nunes</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CIN7404</t>
+          <t>CIN7412</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>04342C</t>
+          <t>04342A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Planejamento Estratégico</t>
+          <t>Marketing da Informação</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4ª Fase</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2684,49 +2684,49 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>6.2020-2</t>
+          <t>3.1010-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>CED-004 D</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>Sonali Paula Molin Bedin</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CIN7405</t>
+          <t>CIN7501</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>04342A</t>
+          <t>05342</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Projeto de Informatização</t>
+          <t>Arquitetura da Informação e Usabilidade</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4ª Fase</t>
+          <t>5ª Fase</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2746,49 +2746,49 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>5.1010-2</t>
+          <t>2.1830-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Gustavo Medeiros de Araújo</t>
+          <t>Márcio Matias</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CIN7405</t>
+          <t>CIN7502</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>04342C</t>
+          <t>05342</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Projeto de Informatização</t>
+          <t>Mineração de Texto</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>4ª Fase</t>
+          <t>5ª Fase</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2808,49 +2808,49 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>4.2020-2</t>
+          <t>5.2020-2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Gustavo Medeiros de Araújo</t>
+          <t>Flavio Augusto Carraro</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CIN7406</t>
+          <t>CIN7503</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>04342A</t>
+          <t>05342</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Preservação Digital</t>
+          <t>Bancos de Dados</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4ª Fase</t>
+          <t>5ª Fase</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2870,49 +2870,49 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6.0820-2</t>
+          <t>6.2020-2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Camila Schwinden Lehmkuhl</t>
+          <t>Flavio Augusto Carraro</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CIN7406</t>
+          <t>CIN7504</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>04342C</t>
+          <t>05342</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Preservação Digital</t>
+          <t>Gerenciamento de Projetos</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4ª Fase</t>
+          <t>5ª Fase</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2932,17 +2932,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2.2020-2</t>
+          <t>6.1830-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2954,27 +2954,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CIN7412</t>
+          <t>CIN7505</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>04342A</t>
+          <t>05342</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Marketing da Informação</t>
+          <t>Estágio em Ciência da Informação</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2ª Fase</t>
+          <t>5ª Fase</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2984,59 +2984,59 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>432</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>3.1010-2</t>
+          <t>2.1420-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>CED-004 D</t>
+          <t>CED-105 B</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Sonali Paula Molin Bedin</t>
+          <t>Nathalia Berger Werlang</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CIN7412</t>
+          <t>CIN7601</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>04342C</t>
+          <t>06342</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Marketing da Informação</t>
+          <t>Linked Data</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2ª Fase</t>
+          <t>6ª Fase</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3056,49 +3056,49 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>5.2020-2</t>
+          <t>4.1830-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>EF1-EFI301</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>Flavio Augusto Carraro</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CIN7501</t>
+          <t>CIN7602</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>05342</t>
+          <t>06342</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Arquitetura da Informação e Usabilidade</t>
+          <t>Mídias Sociais</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5ª Fase</t>
+          <t>6ª Fase</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3123,44 +3123,44 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2.2020-2</t>
+          <t>6.1830-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>CCE-516B</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Márcio Matias</t>
+          <t>Flavio Augusto Carraro</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CIN7502</t>
+          <t>CIN7603</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>05342</t>
+          <t>06342</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mineração de Texto</t>
+          <t>Empreendedorismo II</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>5ª Fase</t>
+          <t>6ª Fase</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3175,54 +3175,54 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>3.2020-2</t>
+          <t>2.1830-4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>CCE-CCE129</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Flavio Augusto Carraro</t>
+          <t>Nathalia Berger Werlang</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CIN7503</t>
+          <t>CIN7604</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>05342</t>
+          <t>06342</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Bancos de Dados</t>
+          <t>TCC</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5ª Fase</t>
+          <t>6ª Fase</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3237,59 +3237,59 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>6.2020-2</t>
+          <t>4.1620-2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>CCE-CCE131</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Flavio Augusto Carraro</t>
+          <t>Márcio Matias</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CIN7504</t>
+          <t>CIN7903</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>05342</t>
+          <t>06342</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Gerenciamento de Projetos</t>
+          <t>Inteligência Competitiva</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>5ª Fase</t>
+          <t>5ª Fase (Optativa)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Obrigatória</t>
+          <t>Optativa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3304,121 +3304,121 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>6.1830-2</t>
+          <t>3.1830-2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>CCE-CCE129</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>A contratar</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CIN7505</t>
+          <t>CIN7904</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>05342</t>
+          <t>06342</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Estágio em Ciência da Informação</t>
+          <t>Avaliação de Desempenho</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5ª Fase</t>
+          <t>5ª Fase (Optativa)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Obrigatória</t>
+          <t>Optativa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2.1420-2</t>
+          <t>5.1830-2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>CED-105 B</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Nathalia Berger Werlang</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CIN7601</t>
+          <t>CIN7905</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>06342</t>
+          <t>05342</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Linked Data</t>
+          <t>Teoria da Decisão</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6ª Fase</t>
+          <t>6ª Fase (Optativa)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Obrigatória</t>
+          <t>Optativa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3438,39 +3438,39 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>CCE-CCE131</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Flavio Augusto Carraro</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CIN7602</t>
+          <t>CIN7907</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>06342</t>
+          <t>02342</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mídias Sociais</t>
+          <t>Lógica Aplicada I</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6ª Fase</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3485,22 +3485,22 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>6.1830-2</t>
+          <t>3.1830-4</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>CCE-CCE131</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3512,89 +3512,89 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CIN7603</t>
+          <t>CIN7917</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>06342</t>
+          <t>05342</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Empreendedorismo II</t>
+          <t>Visualização da Informação</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6ª Fase</t>
+          <t>5ª Fase (Optativa)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Obrigatória</t>
+          <t>Optativa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2.1830-4</t>
+          <t>4.1830-2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>CCE-CCE129</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Nathalia Berger Werlang</t>
+          <t>Márcio Matias</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CIN7604</t>
+          <t>CIN7925</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>06342</t>
+          <t>01342</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TCC</t>
+          <t>Introdução a Algoritmos</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6ª Fase</t>
+          <t>1ª Fase</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3604,44 +3604,44 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>4.1620-2</t>
+          <t>5.2020-2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>EF1-EFI303</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Márcio Matias</t>
+          <t>Ricardo Alexandre Reinaldo de Moraes</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CIN7904</t>
+          <t>CIN7927</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Avaliação de Desempenho</t>
+          <t>Gestão da Informação Pública</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>5ª Fase (Optativa)</t>
+          <t>Optativa</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3676,49 +3676,49 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>4.1830-2</t>
+          <t>2.1830-2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>CCE-CCE129</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>A contratar</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CIN7906</t>
+          <t>CIN7935</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>05342</t>
+          <t>06342</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Inovação e Informação</t>
+          <t>Liderança e Gerência</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5ª Fase (Optativa)</t>
+          <t>6ª Fase (Optativa)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3733,54 +3733,54 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>3.1830-2 | 5.1830-2</t>
+          <t>5.1830-2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>CCE-CCE129 | CCE-CCE129</t>
+          <t>CED-LBCON</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>Sonali Paula Molin Bedin</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CIN7907</t>
+          <t>CIN7936</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>02342</t>
+          <t>03342A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Lógica Aplicada I</t>
+          <t>Proteção de Dados Pessoais</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2ª Fase</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3790,64 +3790,64 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>5.1830-4</t>
+          <t>2.0820-2</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>CCE-CCE131</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Ricardo Alexandre Reinaldo de Moraes e Flavio Augusto Carraro</t>
+          <t>Marcelo Minghelli</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CIN7913</t>
+          <t>CIN7936</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>04342</t>
+          <t>03342C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Lógica Instrumental II</t>
+          <t>Proteção de Dados Pessoais</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5ª Fase (Optativa)</t>
+          <t>3ª Fase</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>Obrigatória</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3862,49 +3862,49 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>4.1420-2</t>
+          <t>3.1830-2</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>CED-102 C</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Ilson Wilmar Rodrigues Filho</t>
+          <t>Marcelo Minghelli</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CIN7917</t>
+          <t>CIN7938</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>06342</t>
+          <t>05342</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Visualização da Informação</t>
+          <t>Segurança da Informação</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>6ª Fase (Optativa)</t>
+          <t>5ª Fase (Optativa)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3924,59 +3924,59 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>4.1830-2</t>
+          <t>3.2020-2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>CCE-516B</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Márcio Matias</t>
+          <t>A contratar</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CIN7919</t>
+          <t>CIN7943</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>05342</t>
+          <t>01342</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Informação, Direito e Cidadania</t>
+          <t>Experiência do Usuário (UX) User Experience</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>5ª Fase (Optativa)</t>
+          <t>1ª Fase</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>Obrigatória</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3996,49 +3996,49 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>CCE-516B</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Luis Roberto Sousa Mendes</t>
+          <t>Márcio Matias</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CIN7925</t>
+          <t>CIN7945</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>01342</t>
+          <t>05342</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Introdução a Algoritmos</t>
+          <t>Fontes de Informação Tecnológica</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1ª Fase</t>
+          <t>5ª Fase (Optativa)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Obrigatória</t>
+          <t>Optativa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4048,49 +4048,49 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>4.1830-2</t>
+          <t>2.2020-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>CCE-CCE131</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Flavio Augusto Carraro</t>
+          <t>Márcio Matias</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CIN7935</t>
+          <t>CIN7946</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>06342</t>
+          <t>05342</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Liderança e Gerência</t>
+          <t>Pitch de Carreira</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>5ª Fase (Optativa)</t>
+          <t>6ª Fase (Optativa)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4110,34 +4110,34 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2.1830-2</t>
+          <t>5.2020-2</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>CCE-CCE131</t>
+          <t>CED-LBCON</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>Sonali Paula Molin Bedin</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CIN7936</t>
+          <t>HST7921</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Proteção de Dados Pessoais</t>
+          <t>História do Brasil Contemporâneo</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2.0820-2</t>
+          <t>5.0820-4</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4187,19 +4187,19 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Marcelo Minghelli</t>
+          <t>Roselane Neckel</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CIN7936</t>
+          <t>HST7921</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Proteção de Dados Pessoais</t>
+          <t>História do Brasil Contemporâneo</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4239,44 +4239,44 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>4.2020-2</t>
+          <t>6.1830-4</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>CED-102 C</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Marcelo Minghelli</t>
+          <t>Roselane Neckel</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CIN7943</t>
+          <t>INE5111</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>01342</t>
+          <t>02342A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Experiência do Usuário (UX) User Experience</t>
+          <t>Estatística Aplicada I</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1ª Fase</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4286,183 +4286,183 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>4.2020-2</t>
+          <t>3.0820-2 | 4.1010-2</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>CCE-CCE131</t>
+          <t>CED-LBPREV | CED-LBPREV</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Márcio Matias</t>
+          <t>Vera do Carmo Comparsi de Vargas</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CIN7944</t>
+          <t>INE5111</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>06342</t>
+          <t>02342C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Curadoria Digital</t>
+          <t>Estatística Aplicada I</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>6ª Fase (Optativa)</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>Obrigatória</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>4.2020-2</t>
+          <t>2.1830-2 | 5.1830-2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>CCE-CCE129</t>
+          <t>CED-LBPREV | CED-102 C</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Flavio Augusto Carraro</t>
+          <t>Manoella Reis Cardenuto</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CIN7945</t>
+          <t>LLV7802</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>05342</t>
+          <t>01342C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Fontes de Informação Tecnológica</t>
+          <t>Leitura e Produção do Texto</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>1ª Fase</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>Obrigatória</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Específico</t>
+          <t>Comum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2.1830-2</t>
+          <t>6.1830-4</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>CCE-516B</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Márcio Matias</t>
+          <t>Gabriela Rempel</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HST7921</t>
+          <t>LLV7802</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>03342A</t>
+          <t>01342D</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>História do Brasil Contemporâneo</t>
+          <t>Leitura e Produção do Texto</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>3ª Fase</t>
+          <t>1ª Fase</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4487,44 +4487,44 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>5.0820-4</t>
+          <t>6.1830-4</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Roselane Neckel</t>
+          <t>Silvia Ines Coneglian Carrilho de Vasconcelos</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026.1</t>
+          <t>2026.2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HST7921</t>
+          <t>MTM3110</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>03342C</t>
+          <t>01342</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>História do Brasil Contemporâneo</t>
+          <t>Cálculo</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>3ª Fase</t>
+          <t>1ª Fase</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4534,342 +4534,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>Específico</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>6.1830-4</t>
+          <t>3.1830-2 | 5.1830-2</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>CFH-1FH322</t>
+          <t>AUX-ALOCAR | AUX-ALOCAR</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Roselane Neckel</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026.1</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>INE5111</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>04342A</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Estatística Aplicada I</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2ª Fase</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Obrigatória</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Comum</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>3.0820-2 | 4.1010-2</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>CED-LBPREV | CED-LBPREV</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Vera do Carmo Comparsi de Vargas</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026.1</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>INE5111</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>04342C</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Estatística Aplicada I</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>2ª Fase</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Obrigatória</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Comum</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>2.1830-2 | 5.1830-2</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>CTC-CTC106 | CTC-CTC106</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Manoella Reis Cardenuto</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026.1</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>LLV7802</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>01342C</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Leitura e Produção do Texto</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>1ª Fase</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Obrigatória</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Comum</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>6.1830-4</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>EF1-EFI304</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Graziela Hahn</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026.1</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>LLV7802</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>01342D</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Leitura e Produção do Texto</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>1ª Fase</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Obrigatória</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Comum</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>6.1830-4</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>EF1-EFI304</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Graziela Hahn</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026.1</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>MTM3110</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>01342</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Cálculo</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>1ª Fase</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Obrigatória</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Específico</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>3.1830-2 | 5.1830-2</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>EF1-EFI405 | EF1-EFI405</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Camilo Campana e Camila Aparecida Benedito Rodrigues de Lima</t>
+          <t>Francisco Carlos Caramello Junior</t>
         </is>
       </c>
     </row>
@@ -4884,14 +4574,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="63" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -5159,22 +4849,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>CIN7144 (01342)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5191,22 +4881,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>CIN7145 (01342)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5223,22 +4913,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CIN7145 (01342)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5255,7 +4945,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CAD5103 (01342C) / CAD5103 (01342D)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5265,7 +4955,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CIN7925 (01342)</t>
+          <t>CIN7141 (01342C)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5287,7 +4977,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CAD5103 (01342C) / CAD5103 (01342D)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5297,7 +4987,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CIN7925 (01342)</t>
+          <t>CIN7141 (01342C)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5319,7 +5009,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CAD5103 (01342C) / CAD5103 (01342D)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5334,7 +5024,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CIN7141 (01342C)</t>
+          <t>CIN7925 (01342)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -5351,7 +5041,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CAD5103 (01342C) / CAD5103 (01342D)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5366,7 +5056,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CIN7141 (01342C)</t>
+          <t>CIN7925 (01342)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5409,198 +5099,242 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CIN7141 (01342C)</t>
+          <t>CAD5103 (01342C)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lógica Instrumental I</t>
+          <t>Administração I</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CCE-CCE129</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ilson Wilmar Rodrigues Filho</t>
+          <t>Monica Scoz Mendes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CIN7143 (01342C)</t>
+          <t>CAD5103 (01342D)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Empreendedorismo I</t>
+          <t>Administração I</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EF1-EFI402</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>?</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CIN7144 (01342)</t>
+          <t>CIN7141 (01342C)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tutoria Acadêmica I</t>
+          <t>Lógica Instrumental I</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ricardo Alexandre Reinaldo de Moraes</t>
+          <t>Ilson Wilmar Rodrigues Filho</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CIN7145 (01342)</t>
+          <t>CIN7143 (01342C)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Gestão da Informação</t>
+          <t>Empreendedorismo I</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CED-103 C</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Nathalia Berger Werlang</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CIN7925 (01342)</t>
+          <t>CIN7144 (01342)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Introdução a Algoritmos</t>
+          <t>Tutoria Acadêmica I</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CCE-CCE131</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Flavio Augusto Carraro</t>
+          <t>Ricardo Alexandre Reinaldo de Moraes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CIN7943 (01342)</t>
+          <t>CIN7145 (01342)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Experiência do Usuário (UX) User Experience</t>
+          <t>Gestão da Informação</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CCE-CCE131</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Márcio Matias</t>
+          <t>Nathalia Berger Werlang</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LLV7802 (01342C)</t>
+          <t>CIN7925 (01342)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Leitura e Produção do Texto</t>
+          <t>Introdução a Algoritmos</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EF1-EFI304</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Graziela Hahn</t>
+          <t>Ricardo Alexandre Reinaldo de Moraes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LLV7802 (01342D)</t>
+          <t>CIN7943 (01342)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Leitura e Produção do Texto</t>
+          <t>Experiência do Usuário (UX) User Experience</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EF1-EFI304</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Graziela Hahn</t>
+          <t>Márcio Matias</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>LLV7802 (01342C)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Leitura e Produção do Texto</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AUX-ALOCAR</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Gabriela Rempel</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LLV7802 (01342D)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Leitura e Produção do Texto</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AUX-ALOCAR</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Silvia Ines Coneglian Carrilho de Vasconcelos</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>MTM3110 (01342)</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Cálculo</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>EF1-EFI405 | EF1-EFI405</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Camilo Campana e Camila Aparecida Benedito Rodrigues de Lima</t>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AUX-ALOCAR | AUX-ALOCAR</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Francisco Carlos Caramello Junior</t>
         </is>
       </c>
     </row>
@@ -5619,14 +5353,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="64" customWidth="1" min="4" max="4"/>
-    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -5685,7 +5419,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CIN7203 (02342A)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -5702,12 +5436,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CIN7206 (02342A)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CIN7202 (02342A) / INE5111 (04342A)</t>
+          <t>INE5111 (02342A)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5717,12 +5451,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CIN7203 (02342A)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CIN7201 (02342A)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5468,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CIN7206 (02342A)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CIN7202 (02342A) / INE5111 (04342A)</t>
+          <t>INE5111 (02342A)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5754,7 +5488,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CIN7201 (02342A)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5505,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CIN7206 (02342A) / CIN7412 (04342A)</t>
+          <t>CIN7412 (04342A)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>INE5111 (04342A)</t>
+          <t>INE5111 (02342A)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5786,7 +5520,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CIN7201 (02342A)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5803,12 +5537,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CIN7206 (02342A) / CIN7412 (04342A)</t>
+          <t>CIN7412 (04342A)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>INE5111 (04342A)</t>
+          <t>INE5111 (02342A)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5818,7 +5552,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CIN7201 (02342A)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5596,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CIN7205 (02342B)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5894,7 +5628,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CIN7205 (02342B)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5926,7 +5660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CIN7205 (02342B)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5958,7 +5692,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CIN7205 (02342B)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5968,12 +5702,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CIN7204 (02342C)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5990,22 +5724,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INE5111 (04342C)</t>
+          <t>INE5111 (02342C)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CIN7206 (02342C)</t>
+          <t>CIN7907 (02342)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CIN7203 (02342C)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CIN7907 (02342) / INE5111 (04342C)</t>
+          <t>INE5111 (02342C)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -6022,22 +5756,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INE5111 (04342C)</t>
+          <t>INE5111 (02342C)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CIN7206 (02342C)</t>
+          <t>CIN7907 (02342)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CIN7203 (02342C)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CIN7907 (02342) / INE5111 (04342C)</t>
+          <t>INE5111 (02342C)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -6059,17 +5793,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CIN7206 (02342C)</t>
+          <t>CIN7907 (02342)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CIN7202 (02342C)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CIN7412 (04342C) / CIN7907 (02342)</t>
+          <t>CIN7412 (02342C)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -6091,17 +5825,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CIN7206 (02342C)</t>
+          <t>CIN7907 (02342)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CIN7202 (02342C)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CIN7412 (04342C) / CIN7907 (02342)</t>
+          <t>CIN7412 (02342C)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -6144,7 +5878,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CIN7201 (02342A)</t>
+          <t>CIN7201 (02342C)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6154,7 +5888,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CED-004 D</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6166,306 +5900,130 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CIN7201 (02342C)</t>
+          <t>CIN7204 (02342C)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sistemas de Organização do Conhecimento</t>
+          <t>Tutoria Acadêmica II</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EF1-EFI405</t>
+          <t>CED-D109</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
+          <t>Ricardo Alexandre Reinaldo de Moraes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CIN7202 (02342A)</t>
+          <t>CIN7412 (02342C)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sociedade da Informação</t>
+          <t>Marketing da Informação</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Enrique Muriel Torrado</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CIN7202 (02342C)</t>
+          <t>CIN7412 (04342A)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sociedade da Informação</t>
+          <t>Marketing da Informação</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EF1-EFI305</t>
+          <t>CED-004 D</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Enrique Muriel Torrado</t>
+          <t>Sonali Paula Molin Bedin</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CIN7203 (02342A)</t>
+          <t>CIN7907 (02342)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ética Profissional</t>
+          <t>Lógica Aplicada I</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CED-004 D</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
+          <t>Flavio Augusto Carraro</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CIN7203 (02342C)</t>
+          <t>INE5111 (02342A)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ética Profissional</t>
+          <t>Estatística Aplicada I</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EF1-EFI304</t>
+          <t>CED-LBPREV | CED-LBPREV</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
+          <t>Vera do Carmo Comparsi de Vargas</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CIN7204 (02342C)</t>
+          <t>INE5111 (02342C)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tutoria Acadêmica II</t>
+          <t>Estatística Aplicada I</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CED-105 B</t>
+          <t>CED-LBPREV | CED-102 C</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
-        <is>
-          <t>Ricardo Alexandre Reinaldo de Moraes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>CIN7205 (02342B)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Recuperação da Informação</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CCE-516B</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>CIN7206 (02342A)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Fontes Gerais de Informação</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CED-102 C | CED-102 C</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Aline Carmes Krüger</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>CIN7206 (02342C)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Fontes Gerais de Informação</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CED-LBPREV</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Patricia da Silva Neubert</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>CIN7412 (04342A)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Marketing da Informação</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CED-004 D</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Sonali Paula Molin Bedin</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>CIN7412 (04342C)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Marketing da Informação</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>EF1-EFI301</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>CIN7907 (02342)</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Lógica Aplicada I</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CCE-CCE131</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Ricardo Alexandre Reinaldo de Moraes e Flavio Augusto Carraro</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>INE5111 (04342A)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Estatística Aplicada I</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CED-LBPREV | CED-LBPREV</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Vera do Carmo Comparsi de Vargas</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>INE5111 (04342C)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Estatística Aplicada I</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CTC-CTC106 | CTC-CTC106</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
         <is>
           <t>Manoella Reis Cardenuto</t>
         </is>
@@ -6491,8 +6049,8 @@
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
@@ -6574,12 +6132,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CIN7301 (03342A)</t>
+          <t>CIN7304 (03342A)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CIN7304 (03342A)</t>
+          <t>CIN7309 (03342A)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -6606,12 +6164,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CIN7301 (03342A)</t>
+          <t>CIN7304 (03342A)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CIN7304 (03342A)</t>
+          <t>CIN7309 (03342A)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6638,7 +6196,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CIN7309 (03342A)</t>
+          <t>CIN7301 (03342A)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6670,7 +6228,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CIN7309 (03342A)</t>
+          <t>CIN7301 (03342A)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -6862,17 +6420,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CIN7309 (03342C)</t>
+          <t>CIN7936 (03342C)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CIN7309 (03342C)</t>
+          <t>CIN7309 (02342C)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CIN7301 (03342C)</t>
+          <t>CIN7302 (03342C)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -6894,17 +6452,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CIN7309 (03342C)</t>
+          <t>CIN7936 (03342C)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CIN7309 (03342C)</t>
+          <t>CIN7309 (02342C)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CIN7301 (03342C)</t>
+          <t>CIN7302 (03342C)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -6926,12 +6484,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CIN7302 (03342C)</t>
+          <t>CIN7301 (03342C)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CIN7936 (03342C)</t>
+          <t>CIN7309 (02342C)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6958,12 +6516,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CIN7302 (03342C)</t>
+          <t>CIN7301 (03342C)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CIN7936 (03342C)</t>
+          <t>CIN7309 (02342C)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7021,7 +6579,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CFH-1FH330</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -7043,12 +6601,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EF1-EFI304</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Callu Ribeiro Ferreira Pedreira e Andrade Bamberg</t>
+          <t>?</t>
         </is>
       </c>
     </row>
@@ -7070,7 +6628,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Elizete Vieira Vitorino e Maria Zanela</t>
+          <t>Maria Zanela</t>
         </is>
       </c>
     </row>
@@ -7087,12 +6645,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EF1-EFI401</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mariana Xavier de Oliveira</t>
+          <t>Edgar Bisset Alvarez</t>
         </is>
       </c>
     </row>
@@ -7136,7 +6694,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Maria Zanela e Elizete Vieira Vitorino</t>
+          <t>Maria Zanela</t>
         </is>
       </c>
     </row>
@@ -7153,7 +6711,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -7202,7 +6760,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Maria Zanela e Elizete Vieira Vitorino</t>
+          <t>Maria Zanela</t>
         </is>
       </c>
     </row>
@@ -7224,14 +6782,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Maria Zanela e Elizete Vieira Vitorino</t>
+          <t>Maria Zanela</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CIN7309 (03342A)</t>
+          <t>CIN7309 (02342C)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7241,19 +6799,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CED-LBTEC | CED-LBTEC</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Rogerio da Silva Nunes</t>
+          <t>?</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CIN7309 (03342C)</t>
+          <t>CIN7309 (03342A)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7263,12 +6821,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CED-LBTEC | CED-LBTEC</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Rogerio da Silva Nunes</t>
+          <t>?</t>
         </is>
       </c>
     </row>
@@ -7351,7 +6909,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CFH-1FH322</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7380,7 +6938,7 @@
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
@@ -7436,7 +6994,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7404 (04342A)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7446,7 +7004,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7404 (04342A)</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7026,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CIN7404 (04342A)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7500,7 +7058,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CIN7404 (04342A)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -7692,7 +7250,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CIN7403 (04342B)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -7714,7 +7272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7403 (04342C)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7724,7 +7282,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CIN7403 (04342B)</t>
+          <t>CIN7403 (04342C)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -7988,7 +7546,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CIN7403 (04342B)</t>
+          <t>CIN7403 (04342C)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7998,7 +7556,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CED-004 D</t>
+          <t>CED-LBPREV | CED-LBPREV</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -8020,12 +7578,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>CED-103 C | CED-103 C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Rogerio da Silva Nunes</t>
+          <t>Maria Zanela</t>
         </is>
       </c>
     </row>
@@ -8069,7 +7627,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Gustavo Medeiros de Araújo</t>
+          <t>Flavio Augusto Carraro</t>
         </is>
       </c>
     </row>
@@ -8086,12 +7644,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Gustavo Medeiros de Araújo</t>
+          <t>Flavio Augusto Carraro</t>
         </is>
       </c>
     </row>
@@ -8113,7 +7671,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Camila Schwinden Lehmkuhl</t>
+          <t>Enrique Muriel Torrado</t>
         </is>
       </c>
     </row>
@@ -8159,7 +7717,7 @@
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -8407,7 +7965,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CIN7913 (04342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -8439,7 +7997,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CIN7913 (04342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8525,22 +8083,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CIN7935 (06342)</t>
+          <t>CIN7501 (05342)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CIN7906 (05342)</t>
+          <t>CIN7903 (06342)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CIN7904 (05342)</t>
+          <t>CIN7917 (05342)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CIN7906 (05342)</t>
+          <t>CIN7904 (06342)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -8557,22 +8115,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CIN7935 (06342)</t>
+          <t>CIN7501 (05342)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CIN7906 (05342)</t>
+          <t>CIN7903 (06342)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CIN7904 (05342)</t>
+          <t>CIN7917 (05342)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CIN7906 (05342)</t>
+          <t>CIN7904 (06342)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -8589,22 +8147,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CIN7501 (05342)</t>
+          <t>CIN7945 (05342)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>CIN7938 (05342)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CIN7502 (05342)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CIN7919 (05342)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -8621,22 +8179,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CIN7501 (05342)</t>
+          <t>CIN7945 (05342)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>CIN7938 (05342)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>CIN7502 (05342)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CIN7919 (05342)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -8689,7 +8247,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CCE-516B</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -8711,7 +8269,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CCE-CCE129</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -8733,7 +8291,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CCE-CCE131</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -8755,7 +8313,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CCE-CCE129</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -8789,17 +8347,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CIN7904 (05342)</t>
+          <t>CIN7903 (06342)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Avaliação de Desempenho</t>
+          <t>Inteligência Competitiva</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CCE-CCE129</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -8811,17 +8369,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CIN7906 (05342)</t>
+          <t>CIN7904 (06342)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Inovação e Informação</t>
+          <t>Avaliação de Desempenho</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CCE-CCE129 | CCE-CCE129</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -8833,66 +8391,66 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CIN7913 (04342)</t>
+          <t>CIN7917 (05342)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lógica Instrumental II</t>
+          <t>Visualização da Informação</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ilson Wilmar Rodrigues Filho</t>
+          <t>Márcio Matias</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CIN7919 (05342)</t>
+          <t>CIN7938 (05342)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Informação, Direito e Cidadania</t>
+          <t>Segurança da Informação</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CCE-516B</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Luis Roberto Sousa Mendes</t>
+          <t>?</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CIN7935 (06342)</t>
+          <t>CIN7945 (05342)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Liderança e Gerência</t>
+          <t>Fontes de Informação Tecnológica</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CCE-CCE131</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>Márcio Matias</t>
         </is>
       </c>
     </row>
@@ -8911,14 +8469,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -9287,17 +8845,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>CIN7905 (05342)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>CIN7601 (06342)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CIN7917 (06342)</t>
-        </is>
-      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7935 (06342)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -9319,17 +8877,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>CIN7905 (05342)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>CIN7601 (06342)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CIN7917 (06342)</t>
-        </is>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7935 (06342)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -9356,12 +8914,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CIN7944 (06342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7946 (05342)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -9388,12 +8946,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CIN7944 (06342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7946 (05342)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -9446,7 +9004,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CCE-CCE131</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -9468,7 +9026,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CCE-CCE131</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -9490,7 +9048,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CCE-CCE129</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -9512,7 +9070,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EF1-EFI303</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -9524,44 +9082,66 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CIN7917 (06342)</t>
+          <t>CIN7905 (05342)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Visualização da Informação</t>
+          <t>Teoria da Decisão</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CCE-516B</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Márcio Matias</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CIN7944 (06342)</t>
+          <t>CIN7935 (06342)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Curadoria Digital</t>
+          <t>Liderança e Gerência</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CCE-CCE129</t>
+          <t>CED-LBCON</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Flavio Augusto Carraro</t>
+          <t>Sonali Paula Molin Bedin</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CIN7946 (05342)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pitch de Carreira</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CED-LBCON</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sonali Paula Molin Bedin</t>
         </is>
       </c>
     </row>

--- a/resultados/relatorio_final.xlsx
+++ b/resultados/relatorio_final.xlsx
@@ -151,8 +151,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Legenda_Fase_5" displayName="Legenda_Fase_5" ref="A19:D29" headerRowCount="1">
-  <autoFilter ref="A19:D29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Legenda_Fase_5" displayName="Legenda_Fase_5" ref="A19:D28" headerRowCount="1">
+  <autoFilter ref="A19:D28"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
@@ -179,8 +179,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Legenda_Fase_6" displayName="Legenda_Fase_6" ref="A19:D26" headerRowCount="1">
-  <autoFilter ref="A19:D26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Legenda_Fase_6" displayName="Legenda_Fase_6" ref="A19:D27" headerRowCount="1">
+  <autoFilter ref="A19:D27"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
@@ -248,8 +248,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Legenda_Fase_3" displayName="Legenda_Fase_3" ref="A19:D35" headerRowCount="1">
-  <autoFilter ref="A19:D35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Legenda_Fase_3" displayName="Legenda_Fase_3" ref="A19:D34" headerRowCount="1">
+  <autoFilter ref="A19:D34"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
@@ -276,8 +276,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Legenda_Fase_4" displayName="Legenda_Fase_4" ref="A19:D30" headerRowCount="1">
-  <autoFilter ref="A19:D30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Legenda_Fase_4" displayName="Legenda_Fase_4" ref="A19:D34" headerRowCount="1">
+  <autoFilter ref="A19:D34"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Cód. (Turma)"/>
     <tableColumn id="2" name="Nome da Disciplina"/>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3ª Fase</t>
+          <t>2ª Fase</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2ª Fase</t>
+          <t>4ª Fase</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>5ª Fase (Optativa)</t>
+          <t>4ª Fase</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>Obrigatória</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5ª Fase (Optativa)</t>
+          <t>5ª Fase</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6ª Fase (Optativa)</t>
+          <t>6ª Fase</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5ª Fase (Optativa)</t>
+          <t>5ª Fase</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Optativa</t>
+          <t>6ª Fase</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>6ª Fase (Optativa)</t>
+          <t>5ª Fase</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>5ª Fase (Optativa)</t>
+          <t>6ª Fase</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>5ª Fase (Optativa)</t>
+          <t>5ª Fase</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>6ª Fase (Optativa)</t>
+          <t>6ª Fase</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4560,6 +4560,130 @@
       <c r="L64" t="inlineStr">
         <is>
           <t>Francisco Carlos Caramello Junior</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026.2</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>INE5111</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>02342A</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Estatística Aplicada I</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>4ª Fase</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Obrigatória</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Comum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>3.0820-2 | 4.1010-2</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>CED-LBPREV | CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Vera do Carmo Comparsi de Vargas</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026.2</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>INE5111</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>02342C</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Estatística Aplicada I</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>4ª Fase</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Obrigatória</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Comum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2.1830-2 | 5.1830-2</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>CED-LBPREV | CED-102 C</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Manoella Reis Cardenuto</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5629,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CIN7412 (04342A)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5537,7 +5661,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CIN7412 (04342A)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5734,7 +5858,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7309 (02342C)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5766,7 +5890,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7309 (02342C)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5798,7 +5922,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7309 (02342C)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5830,7 +5954,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7309 (02342C)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5922,29 +6046,29 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CIN7412 (02342C)</t>
+          <t>CIN7309 (02342C)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Marketing da Informação</t>
+          <t>Gestão de Processos Organizacionais</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-LBTEC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>?</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CIN7412 (04342A)</t>
+          <t>CIN7412 (02342C)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5954,12 +6078,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CED-004 D</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sonali Paula Molin Bedin</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6425,7 +6549,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CIN7309 (02342C)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -6457,7 +6581,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CIN7309 (02342C)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6489,7 +6613,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CIN7309 (02342C)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6521,7 +6645,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CIN7309 (02342C)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6789,7 +6913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CIN7309 (02342C)</t>
+          <t>CIN7309 (03342A)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6811,29 +6935,29 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CIN7309 (03342A)</t>
+          <t>CIN7936 (03342A)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gestão de Processos Organizacionais</t>
+          <t>Proteção de Dados Pessoais</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CED-LBTEC</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Marcelo Minghelli</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CIN7936 (03342A)</t>
+          <t>CIN7936 (03342C)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6843,7 +6967,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CED-LBPREV</t>
+          <t>CED-102 C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6855,29 +6979,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CIN7936 (03342C)</t>
+          <t>HST7921 (03342A)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Proteção de Dados Pessoais</t>
+          <t>História do Brasil Contemporâneo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CED-102 C</t>
+          <t>CED-LBPREV</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Marcelo Minghelli</t>
+          <t>Roselane Neckel</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HST7921 (03342A)</t>
+          <t>HST7921 (03342C)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6891,28 +7015,6 @@
         </is>
       </c>
       <c r="D34" t="inlineStr">
-        <is>
-          <t>Roselane Neckel</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>HST7921 (03342C)</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>História do Brasil Contemporâneo</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CED-LBPREV</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
         <is>
           <t>Roselane Neckel</t>
         </is>
@@ -6933,12 +7035,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
@@ -7021,7 +7123,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>INE5111 (02342A)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -7053,7 +7155,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>INE5111 (02342A)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -7085,12 +7187,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7412 (04342A)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>INE5111 (02342A)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -7117,12 +7219,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7412 (04342A)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>INE5111 (02342A)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -7304,12 +7406,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>INE5111 (02342C)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CIN7401 (04342C)</t>
+          <t>CIN7401 (04342C) / CIN7903 (06342)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -7319,7 +7421,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>INE5111 (02342C)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -7336,12 +7438,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>INE5111 (02342C)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CIN7401 (04342C)</t>
+          <t>CIN7401 (04342C) / CIN7903 (06342)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -7351,7 +7453,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>INE5111 (02342C)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -7694,6 +7796,94 @@
       <c r="D30" t="inlineStr">
         <is>
           <t>Sabrina Borges Ramos de Carvalho</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CIN7412 (04342A)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Marketing da Informação</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CED-004 D</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sonali Paula Molin Bedin</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CIN7903 (06342)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Inteligência Competitiva</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AUX-ALOCAR</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>INE5111 (02342A)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Estatística Aplicada I</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CED-LBPREV | CED-LBPREV</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Vera do Carmo Comparsi de Vargas</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>INE5111 (02342C)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Estatística Aplicada I</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CED-LBPREV | CED-102 C</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Manoella Reis Cardenuto</t>
         </is>
       </c>
     </row>
@@ -7712,14 +7902,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -8088,7 +8278,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CIN7903 (06342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -8098,7 +8288,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CIN7904 (06342)</t>
+          <t>CIN7904 (06342) / CIN7935 (06342)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -8120,7 +8310,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CIN7903 (06342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -8130,7 +8320,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CIN7904 (06342)</t>
+          <t>CIN7904 (06342) / CIN7935 (06342)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -8152,7 +8342,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CIN7938 (05342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -8184,7 +8374,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CIN7938 (05342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -8347,12 +8537,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CIN7903 (06342)</t>
+          <t>CIN7904 (06342)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Inteligência Competitiva</t>
+          <t>Avaliação de Desempenho</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -8362,19 +8552,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CIN7904 (06342)</t>
+          <t>CIN7917 (05342)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Avaliação de Desempenho</t>
+          <t>Visualização da Informação</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -8384,41 +8574,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sabrina Borges Ramos de Carvalho</t>
+          <t>Márcio Matias</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CIN7917 (05342)</t>
+          <t>CIN7935 (06342)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Visualização da Informação</t>
+          <t>Liderança e Gerência</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AUX-ALOCAR</t>
+          <t>CED-LBCON</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Márcio Matias</t>
+          <t>Sonali Paula Molin Bedin</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CIN7938 (05342)</t>
+          <t>CIN7945 (05342)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Segurança da Informação</t>
+          <t>Fontes de Informação Tecnológica</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8427,28 +8617,6 @@
         </is>
       </c>
       <c r="D28" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>CIN7945 (05342)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Fontes de Informação Tecnológica</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AUX-ALOCAR</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
         <is>
           <t>Márcio Matias</t>
         </is>
@@ -8469,11 +8637,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -8840,7 +9008,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CIN7603 (06342)</t>
+          <t>CIN7603 (06342) / CIN7927 (05342)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -8855,7 +9023,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CIN7935 (06342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -8872,7 +9040,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CIN7603 (06342)</t>
+          <t>CIN7603 (06342) / CIN7927 (05342)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -8887,7 +9055,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CIN7935 (06342)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -8909,7 +9077,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7938 (05342)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -8941,7 +9109,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CIN7938 (05342)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9104,42 +9272,64 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CIN7935 (06342)</t>
+          <t>CIN7927 (05342)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Liderança e Gerência</t>
+          <t>Gestão da Informação Pública</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CED-LBCON</t>
+          <t>AUX-ALOCAR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sonali Paula Molin Bedin</t>
+          <t>Sabrina Borges Ramos de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>CIN7938 (05342)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Segurança da Informação</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AUX-ALOCAR</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>CIN7946 (05342)</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Pitch de Carreira</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>CED-LBCON</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Sonali Paula Molin Bedin</t>
         </is>
